--- a/data/trans_orig/IP05A02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP05A02-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32604</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42856</t>
+          <t>42923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41996</t>
+          <t>42710</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52578</t>
+          <t>52798</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78360</t>
+          <t>78423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93545</t>
+          <t>93242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>17571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30924</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>277</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58180</t>
+          <t>58030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73453</t>
+          <t>72545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67664</t>
+          <t>67456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83593</t>
+          <t>83283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131347</t>
+          <t>131358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153022</t>
+          <t>153985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23114</t>
+          <t>24342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37801</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35997</t>
+          <t>35674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48816</t>
+          <t>47946</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>68834</t>
+          <t>69007</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -1415,49 +1415,49 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4688</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>9471</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4688</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8752</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,31%</t>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>15211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43948</t>
+          <t>43793</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56141</t>
+          <t>55847</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46640</t>
+          <t>46807</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58164</t>
+          <t>57607</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94181</t>
+          <t>94189</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110761</t>
+          <t>110409</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,05%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16997</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20072</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>18203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32437</t>
+          <t>32731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54477</t>
+          <t>54588</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65182</t>
+          <t>64993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59269</t>
+          <t>59080</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69727</t>
+          <t>69499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117717</t>
+          <t>117675</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131957</t>
+          <t>132503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16114</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>15809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29060</t>
+          <t>29514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30198</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38295</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32700</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40587</t>
+          <t>40619</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65500</t>
+          <t>65478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77489</t>
+          <t>76953</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18945</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34523</t>
+          <t>34880</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45062</t>
+          <t>45689</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46417</t>
+          <t>45946</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54758</t>
+          <t>54800</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>84030</t>
+          <t>83892</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97802</t>
+          <t>98177</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,79%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18775</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11840</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>27971</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>90482</t>
+          <t>89836</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>105289</t>
+          <t>106210</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>95087</t>
+          <t>95592</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>110642</t>
+          <t>111399</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>190603</t>
+          <t>190449</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>212599</t>
+          <t>212634</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13181</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26500</t>
+          <t>27180</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27301</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>30999</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49536</t>
+          <t>49852</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>16227</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18153</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15782</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29861</t>
+          <t>29698</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>109695</t>
+          <t>110258</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>127161</t>
+          <t>127533</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>118673</t>
+          <t>118074</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>134756</t>
+          <t>135068</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>231232</t>
+          <t>232678</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>257062</t>
+          <t>257728</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,33%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>26532</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>43860</t>
+          <t>43832</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>38109</t>
+          <t>38839</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>55375</t>
+          <t>54659</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>80694</t>
+          <t>79087</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>489795</t>
+          <t>489259</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>526722</t>
+          <t>524523</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>542766</t>
+          <t>542024</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>577775</t>
+          <t>577766</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1044001</t>
+          <t>1038047</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1092227</t>
+          <t>1090345</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>122278</t>
+          <t>122655</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>157524</t>
+          <t>155323</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>112878</t>
+          <t>112861</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>144748</t>
+          <t>145459</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>242649</t>
+          <t>244949</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>288683</t>
+          <t>291814</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>42615</t>
+          <t>42816</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>23320</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>40613</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>53542</t>
+          <t>53933</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>79156</t>
+          <t>79098</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34002</t>
+          <t>33466</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>44684</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41946</t>
+          <t>41996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53098</t>
+          <t>53255</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78016</t>
+          <t>79780</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95480</t>
+          <t>95445</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,08%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17844</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33678</t>
+          <t>32197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8041</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74661</t>
+          <t>75251</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89289</t>
+          <t>89061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74643</t>
+          <t>74798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89623</t>
+          <t>89937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154400</t>
+          <t>156306</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175661</t>
+          <t>176195</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24416</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32042</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31267</t>
+          <t>31842</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50525</t>
+          <t>50397</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15392</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62751</t>
+          <t>62718</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63979</t>
+          <t>64762</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70510</t>
+          <t>70543</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131152</t>
+          <t>130461</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137933</t>
+          <t>137305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47182</t>
+          <t>46670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60578</t>
+          <t>60395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61138</t>
+          <t>60884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72623</t>
+          <t>73232</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111960</t>
+          <t>111728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130339</t>
+          <t>129971</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13597</t>
+          <t>13771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26761</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17214</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22598</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>39353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35909</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42509</t>
+          <t>42534</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34020</t>
+          <t>33326</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42600</t>
+          <t>42198</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72826</t>
+          <t>73711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83836</t>
+          <t>83935</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>734</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>13026</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49966</t>
+          <t>49976</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55272</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54923</t>
+          <t>55680</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>108430</t>
+          <t>108581</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>114778</t>
+          <t>114769</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>748</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>116311</t>
+          <t>115436</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>128274</t>
+          <t>129003</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>125235</t>
+          <t>124569</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>136780</t>
+          <t>136936</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>245094</t>
+          <t>245647</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>263005</t>
+          <t>262851</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>17270</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>15803</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30785</t>
+          <t>31590</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>121721</t>
+          <t>122789</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>139679</t>
+          <t>139191</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>128372</t>
+          <t>128518</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>146266</t>
+          <t>145829</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>258267</t>
+          <t>258378</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>281101</t>
+          <t>282547</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,28%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>37131</t>
+          <t>36308</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>20795</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>37073</t>
+          <t>37455</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>65962</t>
+          <t>67008</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1533</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>575208</t>
+          <t>576110</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>608876</t>
+          <t>608635</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>615946</t>
+          <t>617197</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>649228</t>
+          <t>649525</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1204146</t>
+          <t>1203438</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1250115</t>
+          <t>1249263</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>77248</t>
+          <t>78182</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>107794</t>
+          <t>108026</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>82243</t>
+          <t>81984</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>112295</t>
+          <t>110869</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>169595</t>
+          <t>167679</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>210366</t>
+          <t>210615</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>34676</t>
+          <t>34987</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>31369</t>
+          <t>31833</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>59967</t>
+          <t>60244</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34245</t>
+          <t>33763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44895</t>
+          <t>45207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39606</t>
+          <t>39528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51702</t>
+          <t>51500</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77563</t>
+          <t>77845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93237</t>
+          <t>93425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,68%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21138</t>
+          <t>21858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36376</t>
+          <t>36125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75812</t>
+          <t>75425</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88772</t>
+          <t>89319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85339</t>
+          <t>85385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97851</t>
+          <t>98471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165005</t>
+          <t>166142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183727</t>
+          <t>183717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>23248</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21066</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21638</t>
+          <t>22812</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37748</t>
+          <t>38583</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60485</t>
+          <t>60003</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66135</t>
+          <t>66136</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59317</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67167</t>
+          <t>67090</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>122939</t>
+          <t>122127</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131834</t>
+          <t>131792</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>11120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51915</t>
+          <t>52478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64375</t>
+          <t>65222</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58304</t>
+          <t>58739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70472</t>
+          <t>71217</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115237</t>
+          <t>114161</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132804</t>
+          <t>132293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29663</t>
+          <t>30824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35023</t>
+          <t>35601</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41616</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37899</t>
+          <t>37770</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44272</t>
+          <t>44360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>75819</t>
+          <t>75838</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84475</t>
+          <t>84913</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47903</t>
+          <t>47684</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53550</t>
+          <t>53538</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>48135</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55543</t>
+          <t>55449</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>98672</t>
+          <t>98020</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>107741</t>
+          <t>107733</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>113990</t>
+          <t>113011</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>125993</t>
+          <t>126465</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>120549</t>
+          <t>121231</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>133372</t>
+          <t>133775</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>239793</t>
+          <t>239728</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>257437</t>
+          <t>257474</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21177</t>
+          <t>21088</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>19265</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34732</t>
+          <t>35375</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>149142</t>
+          <t>149054</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>158902</t>
+          <t>158895</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>159735</t>
+          <t>159362</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>167938</t>
+          <t>168012</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>311512</t>
+          <t>312470</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>324818</t>
+          <t>324688</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>12312</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>11487</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>20694</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -12831,82 +12831,82 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2178</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
           <t>663</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>5890</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>2178</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>596995</t>
+          <t>599072</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>626683</t>
+          <t>627971</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>638895</t>
+          <t>641013</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>668563</t>
+          <t>668334</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1246679</t>
+          <t>1246999</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1290319</t>
+          <t>1289294</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>57032</t>
+          <t>55672</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>84465</t>
+          <t>81362</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>61814</t>
+          <t>61891</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>89110</t>
+          <t>88419</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>123801</t>
+          <t>124140</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>162698</t>
+          <t>161926</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>29274</t>
+          <t>28829</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>28154</t>
+          <t>27240</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>48265</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -13753,7 +13753,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68875</t>
+          <t>68901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148063</t>
+          <t>147503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41704</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111876</t>
+          <t>111598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103799</t>
+          <t>103622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118316</t>
+          <t>118719</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131317</t>
+          <t>134085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>226024</t>
+          <t>225126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15076</t>
+          <t>15014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85586</t>
+          <t>88830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>23974</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>28357</t>
+          <t>29099</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>122257</t>
+          <t>120589</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14455,7 +14455,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49381</t>
+          <t>49553</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55936</t>
+          <t>56127</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54963</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63299</t>
+          <t>63620</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107582</t>
+          <t>107600</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118335</t>
+          <t>117942</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,47 +14793,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3556</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1543</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7231</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3556</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1475</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6836</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56162</t>
+          <t>55727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66065</t>
+          <t>65438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64296</t>
+          <t>64341</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75520</t>
+          <t>75478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124547</t>
+          <t>124057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138889</t>
+          <t>138891</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -15612,7 +15612,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37399</t>
+          <t>36863</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72249</t>
+          <t>72318</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15745,7 +15745,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36919</t>
+          <t>36556</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46204</t>
+          <t>46432</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53396</t>
+          <t>53628</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>85855</t>
+          <t>85964</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95304</t>
+          <t>95716</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8639</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>98507</t>
+          <t>100013</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>112208</t>
+          <t>112363</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>112695</t>
+          <t>112096</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>134258</t>
+          <t>134304</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>217197</t>
+          <t>217554</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>243055</t>
+          <t>242689</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>29409</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36803</t>
+          <t>37861</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>13879</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32081</t>
+          <t>32277</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>119165</t>
+          <t>119725</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>128741</t>
+          <t>128719</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>143676</t>
+          <t>142666</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>153008</t>
+          <t>152862</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>266985</t>
+          <t>266261</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>279814</t>
+          <t>279431</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>440</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>506069</t>
+          <t>498731</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>609467</t>
+          <t>609546</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>671444</t>
+          <t>669819</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>703641</t>
+          <t>702991</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1183095</t>
+          <t>1190782</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1300444</t>
+          <t>1302075</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39850</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>145553</t>
+          <t>153373</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>67091</t>
+          <t>69011</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>88985</t>
+          <t>88332</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>210298</t>
+          <t>201352</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>27484</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>49076</t>
+          <t>48426</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
